--- a/data/trans_dic/PCS12_SP_R3-Clase-trans_dic.xlsx
+++ b/data/trans_dic/PCS12_SP_R3-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil (49.019) de la puntuación del componente de salud física (SF12)</t>
+          <t>Población en el primer cuartil (49.019) de la puntuación del componente de salud física (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,24; 15,51</t>
+          <t>9,42; 15,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,93; 17,37</t>
+          <t>9,92; 16,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,57; 17,83</t>
+          <t>10,58; 17,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,93; 16,63</t>
+          <t>11,01; 16,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,89; 23,28</t>
+          <t>14,31; 22,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,4; 19,79</t>
+          <t>11,28; 19,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,56; 19,88</t>
+          <t>11,34; 19,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,54; 22,72</t>
+          <t>17,09; 23,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,97; 16,77</t>
+          <t>12,0; 17,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,48; 16,69</t>
+          <t>11,46; 16,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,98; 17,2</t>
+          <t>12,14; 17,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,47; 18,68</t>
+          <t>14,64; 18,7</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,17; 12,64</t>
+          <t>6,48; 12,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,73; 19,29</t>
+          <t>11,54; 19,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,44; 15,35</t>
+          <t>8,45; 15,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,49; 21,07</t>
+          <t>14,76; 21,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,6; 16,35</t>
+          <t>9,38; 16,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,67; 18,9</t>
+          <t>10,17; 18,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,56; 18,96</t>
+          <t>10,44; 18,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,11; 24,77</t>
+          <t>18,4; 25,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,78; 13,61</t>
+          <t>8,73; 13,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,26; 17,45</t>
+          <t>12,14; 17,61</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,18; 15,47</t>
+          <t>10,24; 15,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,05; 21,88</t>
+          <t>17,14; 21,98</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,89; 19,31</t>
+          <t>13,06; 19,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,51; 25,59</t>
+          <t>18,54; 25,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,47; 22,02</t>
+          <t>15,53; 21,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,42; 83,45</t>
+          <t>23,82; 81,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,58; 34,67</t>
+          <t>20,99; 35,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,68; 36,03</t>
+          <t>23,49; 35,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,77; 38,12</t>
+          <t>23,11; 38,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,81; 45,83</t>
+          <t>34,59; 46,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,82; 21,83</t>
+          <t>15,95; 21,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,32; 27,23</t>
+          <t>21,19; 27,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,53; 24,99</t>
+          <t>18,37; 24,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>28,3; 78,93</t>
+          <t>28,55; 78,21</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,64; 23,35</t>
+          <t>18,73; 23,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,56; 23,68</t>
+          <t>18,55; 23,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,05; 21,75</t>
+          <t>16,87; 21,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,65; 29,49</t>
+          <t>23,83; 29,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,8; 25,9</t>
+          <t>19,93; 26,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,82; 23,4</t>
+          <t>17,57; 23,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,81; 22,39</t>
+          <t>16,57; 22,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,98; 27,4</t>
+          <t>10,45; 27,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,01; 23,5</t>
+          <t>19,9; 23,53</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,62; 22,69</t>
+          <t>18,88; 22,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,59; 21,08</t>
+          <t>17,69; 21,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,84; 27,22</t>
+          <t>16,28; 27,29</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,81; 24,25</t>
+          <t>15,8; 24,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,91; 22,62</t>
+          <t>15,91; 23,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,18; 25,85</t>
+          <t>19,13; 25,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,72; 33,75</t>
+          <t>24,67; 32,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,53; 32,16</t>
+          <t>24,42; 31,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,06; 41,95</t>
+          <t>34,6; 41,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,36; 36,34</t>
+          <t>29,04; 36,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,26; 39,9</t>
+          <t>26,6; 40,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,82; 27,69</t>
+          <t>22,07; 28,04</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27,89; 33,23</t>
+          <t>28,18; 33,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,45; 30,67</t>
+          <t>25,63; 30,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,1; 36,22</t>
+          <t>26,82; 35,93</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,4</t>
+          <t>1,95; 6,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,29; 7,66</t>
+          <t>2,65; 8,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,16</t>
+          <t>0,94; 5,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,96</t>
+          <t>1,98; 7,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,11; 38,5</t>
+          <t>33,02; 38,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,17; 40,34</t>
+          <t>34,51; 40,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,2; 36,53</t>
+          <t>30,36; 36,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33,1; 39,17</t>
+          <t>33,31; 39,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27,21; 32,01</t>
+          <t>27,32; 31,87</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28,34; 33,78</t>
+          <t>28,42; 33,52</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24,49; 29,47</t>
+          <t>24,45; 29,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25,88; 31,25</t>
+          <t>25,62; 31,2</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,65; 17,16</t>
+          <t>14,56; 17,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,53; 19,34</t>
+          <t>16,51; 19,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,43; 18,13</t>
+          <t>15,38; 17,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21,08; 44,6</t>
+          <t>21,11; 45,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,75; 28,7</t>
+          <t>25,56; 28,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,56; 30,52</t>
+          <t>27,6; 30,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,46; 27,56</t>
+          <t>24,53; 27,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,26; 30,88</t>
+          <t>22,85; 30,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,5; 22,65</t>
+          <t>20,61; 22,56</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22,5; 24,63</t>
+          <t>22,64; 24,52</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20,45; 22,43</t>
+          <t>20,44; 22,51</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24,49; 36,65</t>
+          <t>24,39; 36,82</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil (49.019) de la puntuación del componente de salud física (SF12)</t>
+          <t>Población en el primer cuartil (49.019) de la puntuación del componente de salud física (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43793; 73497</t>
+          <t>44612; 72986</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43435; 75957</t>
+          <t>43366; 72386</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45338; 76508</t>
+          <t>45389; 73276</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54973; 83633</t>
+          <t>55378; 83018</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>42592; 71409</t>
+          <t>43875; 69741</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35860; 62240</t>
+          <t>35471; 62684</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40113; 69005</t>
+          <t>39366; 68470</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>73791; 101371</t>
+          <t>76260; 102658</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>93390; 130921</t>
+          <t>93677; 132992</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>86279; 125420</t>
+          <t>86157; 126994</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>92995; 133519</t>
+          <t>94263; 134845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>137378; 177354</t>
+          <t>138954; 177480</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22627; 46376</t>
+          <t>23789; 45944</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>49107; 80782</t>
+          <t>48322; 79926</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31848; 57905</t>
+          <t>31861; 57286</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65414; 95150</t>
+          <t>66630; 97423</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35717; 60794</t>
+          <t>34899; 61018</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36077; 63880</t>
+          <t>34384; 62311</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39302; 70594</t>
+          <t>38849; 67966</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69182; 94642</t>
+          <t>70297; 95878</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>64859; 100554</t>
+          <t>64520; 98708</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92762; 132078</t>
+          <t>91883; 133255</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76322; 115984</t>
+          <t>76786; 115137</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>142146; 182339</t>
+          <t>142889; 183209</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>69923; 104733</t>
+          <t>70828; 103648</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>116503; 161094</t>
+          <t>116681; 161103</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80718; 114934</t>
+          <t>81037; 114643</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>162492; 555269</t>
+          <t>158492; 543843</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>34524; 58174</t>
+          <t>35220; 59162</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61604; 93719</t>
+          <t>61096; 91717</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37821; 63323</t>
+          <t>38387; 63811</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>56092; 76034</t>
+          <t>57389; 77036</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>112372; 155065</t>
+          <t>113277; 154699</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>189615; 242239</t>
+          <t>188518; 241725</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>127460; 171961</t>
+          <t>126373; 171121</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>235250; 656163</t>
+          <t>237311; 650176</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>230812; 289129</t>
+          <t>231988; 287944</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>215078; 274487</t>
+          <t>214948; 275533</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>196068; 250030</t>
+          <t>193980; 249057</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>243515; 303667</t>
+          <t>245388; 303148</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>141458; 185013</t>
+          <t>142347; 188566</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>136593; 179429</t>
+          <t>134701; 180145</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>138846; 184934</t>
+          <t>136821; 184472</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>107187; 267422</t>
+          <t>101937; 268561</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>390703; 458949</t>
+          <t>388515; 459485</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>358511; 436960</t>
+          <t>363511; 436514</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>347425; 416342</t>
+          <t>349373; 420359</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>337664; 545996</t>
+          <t>326418; 547344</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>55430; 85002</t>
+          <t>55381; 84472</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>81254; 115510</t>
+          <t>81220; 118434</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>119057; 160475</t>
+          <t>118716; 157729</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>116302; 158768</t>
+          <t>116057; 154798</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>139505; 182920</t>
+          <t>138911; 181808</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>259367; 319483</t>
+          <t>263503; 318777</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>216765; 268305</t>
+          <t>214393; 268829</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>211300; 333811</t>
+          <t>222576; 341511</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>200616; 254524</t>
+          <t>202870; 257789</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>354750; 422784</t>
+          <t>358428; 422715</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>345809; 416825</t>
+          <t>348292; 416051</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>354225; 473487</t>
+          <t>350589; 469681</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5966; 19093</t>
+          <t>5801; 19528</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6118; 20454</t>
+          <t>7084; 21752</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2694; 14823</t>
+          <t>2689; 14344</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4703; 16741</t>
+          <t>4758; 18777</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>413453; 480828</t>
+          <t>412390; 478804</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>379058; 447548</t>
+          <t>382807; 448139</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>326770; 395265</t>
+          <t>328473; 397107</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>249080; 294820</t>
+          <t>250735; 297194</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>420866; 495114</t>
+          <t>422574; 493055</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>389963; 464823</t>
+          <t>391180; 461311</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>335334; 403507</t>
+          <t>334788; 404043</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>256973; 310305</t>
+          <t>254424; 309898</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>479173; 561106</t>
+          <t>476267; 556911</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>565621; 661702</t>
+          <t>564789; 665492</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>522344; 613931</t>
+          <t>520885; 605492</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>708300; 1498972</t>
+          <t>709408; 1541772</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>869997; 969375</t>
+          <t>863377; 966962</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>978280; 1083376</t>
+          <t>979757; 1090113</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>863741; 973278</t>
+          <t>866149; 977511</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>827729; 1098967</t>
+          <t>813239; 1096528</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1363090; 1505973</t>
+          <t>1369962; 1500128</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1569027; 1717149</t>
+          <t>1578502; 1709590</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1414428; 1551368</t>
+          <t>1413901; 1557089</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1694623; 2535770</t>
+          <t>1687675; 2547570</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/PCS12_SP_R3-Clase-trans_dic.xlsx
+++ b/data/trans_dic/PCS12_SP_R3-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,42; 15,41</t>
+          <t>9,19; 15,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,92; 16,56</t>
+          <t>9,97; 16,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,58; 17,08</t>
+          <t>10,54; 17,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,01; 16,5</t>
+          <t>10,85; 16,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,31; 22,74</t>
+          <t>13,65; 22,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,28; 19,93</t>
+          <t>11,1; 19,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,34; 19,73</t>
+          <t>11,54; 19,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,09; 23,01</t>
+          <t>17,14; 23,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,0; 17,04</t>
+          <t>12,18; 17,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,46; 16,89</t>
+          <t>11,5; 16,97</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,14; 17,37</t>
+          <t>12,22; 17,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,64; 18,7</t>
+          <t>14,89; 18,99</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,48; 12,52</t>
+          <t>6,39; 12,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,54; 19,08</t>
+          <t>12,06; 19,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,45; 15,19</t>
+          <t>8,16; 15,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,76; 21,58</t>
+          <t>14,19; 20,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,38; 16,41</t>
+          <t>9,47; 16,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,17; 18,43</t>
+          <t>10,35; 18,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,44; 18,26</t>
+          <t>10,69; 18,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,4; 25,1</t>
+          <t>18,97; 25,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,73; 13,36</t>
+          <t>8,75; 13,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,14; 17,61</t>
+          <t>12,37; 17,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,24; 15,36</t>
+          <t>10,2; 15,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,14; 21,98</t>
+          <t>17,33; 21,9</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>28,71%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,06; 19,11</t>
+          <t>13,39; 19,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,54; 25,6</t>
+          <t>18,48; 25,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,53; 21,97</t>
+          <t>15,46; 22,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,82; 81,74</t>
+          <t>20,87; 28,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,99; 35,26</t>
+          <t>20,88; 35,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,49; 35,26</t>
+          <t>23,8; 35,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,11; 38,41</t>
+          <t>22,71; 37,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,59; 46,43</t>
+          <t>33,29; 44,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,95; 21,78</t>
+          <t>15,94; 21,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,19; 27,17</t>
+          <t>21,2; 27,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,37; 24,87</t>
+          <t>18,67; 25,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>28,55; 78,21</t>
+          <t>25,78; 32,3</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>26,47%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,73; 23,25</t>
+          <t>18,78; 23,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,55; 23,77</t>
+          <t>18,33; 23,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,87; 21,66</t>
+          <t>16,95; 21,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,83; 29,44</t>
+          <t>23,71; 28,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,93; 26,4</t>
+          <t>19,99; 25,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,57; 23,5</t>
+          <t>17,69; 23,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,57; 22,34</t>
+          <t>16,62; 22,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,45; 27,52</t>
+          <t>24,35; 29,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,9; 23,53</t>
+          <t>19,71; 23,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,88; 22,67</t>
+          <t>18,97; 22,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,69; 21,28</t>
+          <t>17,6; 21,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,28; 27,29</t>
+          <t>24,65; 28,33</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,8; 24,1</t>
+          <t>15,68; 24,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,91; 23,2</t>
+          <t>15,56; 22,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,13; 25,41</t>
+          <t>19,31; 26,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,67; 32,9</t>
+          <t>22,78; 30,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,42; 31,97</t>
+          <t>24,95; 32,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,6; 41,86</t>
+          <t>34,59; 41,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,04; 36,41</t>
+          <t>29,04; 36,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>26,6; 40,82</t>
+          <t>35,9; 41,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,07; 28,04</t>
+          <t>22,16; 28,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,18; 33,23</t>
+          <t>27,8; 33,08</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,63; 30,62</t>
+          <t>25,43; 30,46</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,82; 35,93</t>
+          <t>31,28; 36,04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,38%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,55</t>
+          <t>1,94; 6,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,65; 8,15</t>
+          <t>2,37; 7,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,0</t>
+          <t>0,96; 4,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,98; 7,81</t>
+          <t>2,27; 8,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,02; 38,34</t>
+          <t>33,23; 38,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,51; 40,4</t>
+          <t>34,13; 40,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,36; 36,7</t>
+          <t>30,11; 36,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33,31; 39,49</t>
+          <t>32,47; 38,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27,32; 31,87</t>
+          <t>27,2; 31,69</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28,42; 33,52</t>
+          <t>28,09; 33,41</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24,45; 29,51</t>
+          <t>24,25; 29,61</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25,62; 31,2</t>
+          <t>25,86; 31,04</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,56; 17,03</t>
+          <t>14,6; 17,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,51; 19,45</t>
+          <t>16,57; 19,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,38; 17,88</t>
+          <t>15,57; 18,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21,11; 45,88</t>
+          <t>19,75; 22,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,56; 28,62</t>
+          <t>25,63; 28,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,6; 30,71</t>
+          <t>27,49; 30,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,53; 27,68</t>
+          <t>24,53; 27,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>22,85; 30,81</t>
+          <t>29,43; 31,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,61; 22,56</t>
+          <t>20,55; 22,59</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22,64; 24,52</t>
+          <t>22,55; 24,72</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20,44; 22,51</t>
+          <t>20,55; 22,57</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24,39; 36,82</t>
+          <t>25,08; 26,97</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68804</t>
+          <t>75890</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>88045</t>
+          <t>98538</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>156849</t>
+          <t>174429</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>44612; 72986</t>
+          <t>43554; 73511</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43366; 72386</t>
+          <t>43592; 73964</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45389; 73276</t>
+          <t>45247; 75278</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55378; 83018</t>
+          <t>59493; 91768</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>43875; 69741</t>
+          <t>41856; 69303</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35471; 62684</t>
+          <t>34896; 62612</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39366; 68470</t>
+          <t>40066; 68896</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>76260; 102658</t>
+          <t>83453; 112636</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>93677; 132992</t>
+          <t>95030; 134213</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>86157; 126994</t>
+          <t>86452; 127521</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>94263; 134845</t>
+          <t>94873; 135660</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>138954; 177480</t>
+          <t>154133; 196581</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79810</t>
+          <t>82948</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>82101</t>
+          <t>92357</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>161910</t>
+          <t>175306</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23789; 45944</t>
+          <t>23455; 46017</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48322; 79926</t>
+          <t>50520; 80775</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31861; 57286</t>
+          <t>30772; 57660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66630; 97423</t>
+          <t>68418; 99985</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34899; 61018</t>
+          <t>35228; 61006</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34384; 62311</t>
+          <t>34988; 62478</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38849; 67966</t>
+          <t>39783; 67749</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>70297; 95878</t>
+          <t>80149; 106018</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>64520; 98708</t>
+          <t>64623; 98116</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91883; 133255</t>
+          <t>93605; 135929</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76786; 115137</t>
+          <t>76453; 115868</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>142889; 183209</t>
+          <t>156739; 198157</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>350376</t>
+          <t>114983</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>66543</t>
+          <t>73107</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>416919</t>
+          <t>188091</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>70828; 103648</t>
+          <t>72611; 104881</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>116681; 161103</t>
+          <t>116295; 162036</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81037; 114643</t>
+          <t>80711; 115988</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>158492; 543843</t>
+          <t>97792; 133387</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>35220; 59162</t>
+          <t>35032; 59103</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61096; 91717</t>
+          <t>61898; 91790</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38387; 63811</t>
+          <t>37735; 63024</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>57389; 77036</t>
+          <t>62068; 83891</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>113277; 154699</t>
+          <t>113174; 153629</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>188518; 241725</t>
+          <t>188616; 241804</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>126373; 171121</t>
+          <t>128442; 172799</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>237311; 650176</t>
+          <t>168912; 211630</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>273459</t>
+          <t>295249</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>205659</t>
+          <t>230259</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>479118</t>
+          <t>525507</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>231988; 287944</t>
+          <t>232605; 289884</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>214948; 275533</t>
+          <t>212392; 270999</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>193980; 249057</t>
+          <t>194833; 249566</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>245388; 303148</t>
+          <t>266989; 326113</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>142347; 188566</t>
+          <t>142765; 185639</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>134701; 180145</t>
+          <t>135589; 182567</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>136821; 184472</t>
+          <t>137241; 184698</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>101937; 268561</t>
+          <t>209132; 253716</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>388515; 459485</t>
+          <t>384888; 460740</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>363511; 436514</t>
+          <t>365220; 441001</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>349373; 420359</t>
+          <t>347626; 417651</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>326418; 547344</t>
+          <t>489245; 562374</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134474</t>
+          <t>146401</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>294432</t>
+          <t>319319</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>428906</t>
+          <t>465721</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>55381; 84472</t>
+          <t>54962; 85631</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>81220; 118434</t>
+          <t>79470; 115261</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>118716; 157729</t>
+          <t>119829; 162264</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>116057; 154798</t>
+          <t>128264; 169857</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>138911; 181808</t>
+          <t>141921; 186511</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>263503; 318777</t>
+          <t>263385; 318854</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>214393; 268829</t>
+          <t>214358; 267016</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>222576; 341511</t>
+          <t>296507; 341913</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>202870; 257789</t>
+          <t>203681; 258363</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>358428; 422715</t>
+          <t>353607; 420876</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>348292; 416051</t>
+          <t>345534; 413935</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>350589; 469681</t>
+          <t>434421; 500497</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>272576</t>
+          <t>294300</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>281436</t>
+          <t>304337</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5801; 19528</t>
+          <t>5796; 18565</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7084; 21752</t>
+          <t>6332; 20511</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2689; 14344</t>
+          <t>2767; 14296</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4758; 18777</t>
+          <t>5386; 19182</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>412390; 478804</t>
+          <t>414954; 479495</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>382807; 448139</t>
+          <t>378662; 447274</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>328473; 397107</t>
+          <t>325837; 394291</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>250735; 297194</t>
+          <t>271157; 320945</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>422574; 493055</t>
+          <t>420734; 490214</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>391180; 461311</t>
+          <t>386646; 459812</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>334788; 404043</t>
+          <t>332045; 405474</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>254424; 309898</t>
+          <t>277349; 332856</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>915783</t>
+          <t>725508</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1009355</t>
+          <t>1107882</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1925139</t>
+          <t>1833390</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>476267; 556911</t>
+          <t>477509; 560278</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>564789; 665492</t>
+          <t>567003; 662133</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>520885; 605492</t>
+          <t>527055; 611823</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>709408; 1541772</t>
+          <t>676425; 773291</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>863377; 966962</t>
+          <t>865653; 968589</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>979757; 1090113</t>
+          <t>975954; 1084817</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>866149; 977511</t>
+          <t>866154; 975020</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>813239; 1096528</t>
+          <t>1064130; 1156741</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1369962; 1500128</t>
+          <t>1365963; 1501966</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1578502; 1709590</t>
+          <t>1571985; 1723825</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1413901; 1557089</t>
+          <t>1421245; 1560968</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1687675; 2547570</t>
+          <t>1765891; 1898738</t>
         </is>
       </c>
     </row>
